--- a/data/availability/projects/m-squared-developments/mist.xlsx
+++ b/data/availability/projects/m-squared-developments/mist.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -859,7 +859,6 @@
       <c r="G2" t="n">
         <v>157</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -870,7 +869,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -916,7 +915,6 @@
       <c r="G3" t="n">
         <v>157</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -927,7 +925,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -973,7 +971,6 @@
       <c r="G4" t="n">
         <v>80</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -984,7 +981,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1030,7 +1027,6 @@
       <c r="G5" t="n">
         <v>63</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1041,7 +1037,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1087,7 +1083,6 @@
       <c r="G6" t="n">
         <v>157</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1144,7 +1139,6 @@
       <c r="G7" t="n">
         <v>157</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1155,7 +1149,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1201,7 +1195,6 @@
       <c r="G8" t="n">
         <v>134</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1212,7 +1205,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1258,7 +1251,6 @@
       <c r="G9" t="n">
         <v>157</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1269,7 +1261,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1315,7 +1307,6 @@
       <c r="G10" t="n">
         <v>157</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1326,7 +1317,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1372,7 +1363,6 @@
       <c r="G11" t="n">
         <v>134</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1383,7 +1373,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1429,7 +1419,6 @@
       <c r="G12" t="n">
         <v>157</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1440,7 +1429,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1486,7 +1475,6 @@
       <c r="G13" t="n">
         <v>157</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1497,7 +1485,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1543,7 +1531,6 @@
       <c r="G14" t="n">
         <v>180</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1554,7 +1541,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1600,7 +1587,6 @@
       <c r="G15" t="n">
         <v>180</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1611,7 +1597,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1657,7 +1643,6 @@
       <c r="G16" t="n">
         <v>157</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1668,7 +1653,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1714,7 +1699,6 @@
       <c r="G17" t="n">
         <v>157</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1725,7 +1709,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1771,7 +1755,6 @@
       <c r="G18" t="n">
         <v>88</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1782,7 +1765,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1828,7 +1811,6 @@
       <c r="G19" t="n">
         <v>157</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1839,7 +1821,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1885,7 +1867,6 @@
       <c r="G20" t="n">
         <v>157</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1896,7 +1877,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1942,7 +1923,6 @@
       <c r="G21" t="n">
         <v>134</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -1953,7 +1933,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1999,7 +1979,6 @@
       <c r="G22" t="n">
         <v>115</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2010,7 +1989,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2056,7 +2035,6 @@
       <c r="G23" t="n">
         <v>157</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2067,7 +2045,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2113,7 +2091,6 @@
       <c r="G24" t="n">
         <v>157</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2124,7 +2101,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2170,7 +2147,6 @@
       <c r="G25" t="n">
         <v>134</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2181,7 +2157,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2227,7 +2203,6 @@
       <c r="G26" t="n">
         <v>115</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2238,7 +2213,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2284,7 +2259,6 @@
       <c r="G27" t="n">
         <v>157</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2295,7 +2269,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2341,7 +2315,6 @@
       <c r="G28" t="n">
         <v>157</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2352,7 +2325,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2398,7 +2371,6 @@
       <c r="G29" t="n">
         <v>180</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2409,7 +2381,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2455,7 +2427,6 @@
       <c r="G30" t="n">
         <v>115</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2466,7 +2437,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2512,7 +2483,6 @@
       <c r="G31" t="n">
         <v>157</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2523,7 +2493,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2569,7 +2539,6 @@
       <c r="G32" t="n">
         <v>157</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2580,7 +2549,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2626,7 +2595,6 @@
       <c r="G33" t="n">
         <v>134</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2637,7 +2605,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2683,7 +2651,6 @@
       <c r="G34" t="n">
         <v>157</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2694,7 +2661,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2740,7 +2707,6 @@
       <c r="G35" t="n">
         <v>157</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2751,7 +2717,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2797,7 +2763,6 @@
       <c r="G36" t="n">
         <v>157</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2808,7 +2773,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2854,7 +2819,6 @@
       <c r="G37" t="n">
         <v>180</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2865,7 +2829,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2911,7 +2875,6 @@
       <c r="G38" t="n">
         <v>157</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2922,7 +2885,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2968,7 +2931,6 @@
       <c r="G39" t="n">
         <v>157</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -2979,7 +2941,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3025,7 +2987,6 @@
       <c r="G40" t="n">
         <v>115</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3036,7 +2997,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3082,7 +3043,6 @@
       <c r="G41" t="n">
         <v>157</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3093,7 +3053,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3139,7 +3099,6 @@
       <c r="G42" t="n">
         <v>134</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3150,7 +3109,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3196,7 +3155,6 @@
       <c r="G43" t="n">
         <v>157</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3207,7 +3165,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3253,7 +3211,6 @@
       <c r="G44" t="n">
         <v>157</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3264,7 +3221,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3310,7 +3267,6 @@
       <c r="G45" t="n">
         <v>157</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3321,7 +3277,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3367,7 +3323,6 @@
       <c r="G46" t="n">
         <v>157</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3378,7 +3333,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3424,7 +3379,6 @@
       <c r="G47" t="n">
         <v>134</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3435,7 +3389,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3481,7 +3435,6 @@
       <c r="G48" t="n">
         <v>157</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3492,7 +3445,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3538,7 +3491,6 @@
       <c r="G49" t="n">
         <v>157</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3549,7 +3501,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3595,7 +3547,6 @@
       <c r="G50" t="n">
         <v>134</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3606,7 +3557,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3652,7 +3603,6 @@
       <c r="G51" t="n">
         <v>157</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3663,7 +3613,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3709,7 +3659,6 @@
       <c r="G52" t="n">
         <v>157</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3720,7 +3669,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3766,7 +3715,6 @@
       <c r="G53" t="n">
         <v>134</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3777,7 +3725,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3823,7 +3771,6 @@
       <c r="G54" t="n">
         <v>157</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3834,7 +3781,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3880,7 +3827,6 @@
       <c r="G55" t="n">
         <v>157</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3891,7 +3837,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3937,7 +3883,6 @@
       <c r="G56" t="n">
         <v>180</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -3948,7 +3893,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3994,7 +3939,6 @@
       <c r="G57" t="n">
         <v>157</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4005,7 +3949,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4051,7 +3995,6 @@
       <c r="G58" t="n">
         <v>157</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4062,7 +4005,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4108,7 +4051,6 @@
       <c r="G59" t="n">
         <v>88</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4119,7 +4061,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4165,7 +4107,6 @@
       <c r="G60" t="n">
         <v>134</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4176,7 +4117,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4222,7 +4163,6 @@
       <c r="G61" t="n">
         <v>115</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4233,7 +4173,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4279,7 +4219,6 @@
       <c r="G62" t="n">
         <v>157</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4290,7 +4229,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4336,7 +4275,6 @@
       <c r="G63" t="n">
         <v>157</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4347,7 +4285,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4393,7 +4331,6 @@
       <c r="G64" t="n">
         <v>134</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4404,7 +4341,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4450,7 +4387,6 @@
       <c r="G65" t="n">
         <v>146</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4461,7 +4397,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4507,7 +4443,6 @@
       <c r="G66" t="n">
         <v>134</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4518,7 +4453,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4564,7 +4499,6 @@
       <c r="G67" t="n">
         <v>157</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4575,7 +4509,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4621,7 +4555,6 @@
       <c r="G68" t="n">
         <v>157</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4632,7 +4565,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4678,7 +4611,6 @@
       <c r="G69" t="n">
         <v>157</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4689,7 +4621,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4735,7 +4667,6 @@
       <c r="G70" t="n">
         <v>157</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4746,7 +4677,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4792,7 +4723,6 @@
       <c r="G71" t="n">
         <v>134</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4803,7 +4733,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4849,7 +4779,6 @@
       <c r="G72" t="n">
         <v>157</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4860,7 +4789,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4906,7 +4835,6 @@
       <c r="G73" t="n">
         <v>157</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4917,7 +4845,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4963,7 +4891,6 @@
       <c r="G74" t="n">
         <v>134</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -4974,7 +4901,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5020,7 +4947,6 @@
       <c r="G75" t="n">
         <v>134</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5031,7 +4957,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5077,7 +5003,6 @@
       <c r="G76" t="n">
         <v>157</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5088,7 +5013,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5134,7 +5059,6 @@
       <c r="G77" t="n">
         <v>157</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5145,7 +5069,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5191,7 +5115,6 @@
       <c r="G78" t="n">
         <v>134</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5202,7 +5125,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5248,7 +5171,6 @@
       <c r="G79" t="n">
         <v>134</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5259,7 +5181,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5305,7 +5227,6 @@
       <c r="G80" t="n">
         <v>157</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5316,7 +5237,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5362,7 +5283,6 @@
       <c r="G81" t="n">
         <v>157</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5373,7 +5293,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5419,7 +5339,6 @@
       <c r="G82" t="n">
         <v>88</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5430,7 +5349,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5476,7 +5395,6 @@
       <c r="G83" t="n">
         <v>134</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5487,7 +5405,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5533,7 +5451,6 @@
       <c r="G84" t="n">
         <v>115</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5544,7 +5461,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5590,7 +5507,6 @@
       <c r="G85" t="n">
         <v>157</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5601,7 +5517,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5647,7 +5563,6 @@
       <c r="G86" t="n">
         <v>157</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5658,7 +5573,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5704,7 +5619,6 @@
       <c r="G87" t="n">
         <v>134</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5715,7 +5629,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5761,7 +5675,6 @@
       <c r="G88" t="n">
         <v>146</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5772,7 +5685,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5818,7 +5731,6 @@
       <c r="G89" t="n">
         <v>115</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5829,7 +5741,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5875,7 +5787,6 @@
       <c r="G90" t="n">
         <v>157</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5886,7 +5797,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5932,7 +5843,6 @@
       <c r="G91" t="n">
         <v>200</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -5943,7 +5853,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5989,7 +5899,6 @@
       <c r="G92" t="n">
         <v>200</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6000,7 +5909,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6046,7 +5955,6 @@
       <c r="G93" t="n">
         <v>200</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6057,7 +5965,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6103,7 +6011,6 @@
       <c r="G94" t="n">
         <v>200</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6114,7 +6021,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6160,7 +6067,6 @@
       <c r="G95" t="n">
         <v>157</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6171,7 +6077,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6217,7 +6123,6 @@
       <c r="G96" t="n">
         <v>157</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6228,7 +6133,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6274,7 +6179,6 @@
       <c r="G97" t="n">
         <v>134</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6285,7 +6189,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6331,7 +6235,6 @@
       <c r="G98" t="n">
         <v>134</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6342,7 +6245,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6388,7 +6291,6 @@
       <c r="G99" t="n">
         <v>157</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6399,7 +6301,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6445,7 +6347,6 @@
       <c r="G100" t="n">
         <v>157</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6456,7 +6357,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6502,7 +6403,6 @@
       <c r="G101" t="n">
         <v>134</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6513,7 +6413,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6559,7 +6459,6 @@
       <c r="G102" t="n">
         <v>134</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6570,7 +6469,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6616,7 +6515,6 @@
       <c r="G103" t="n">
         <v>157</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6627,7 +6525,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6673,7 +6571,6 @@
       <c r="G104" t="n">
         <v>157</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6684,7 +6581,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6730,7 +6627,6 @@
       <c r="G105" t="n">
         <v>134</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6741,7 +6637,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6787,7 +6683,6 @@
       <c r="G106" t="n">
         <v>146</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6798,7 +6693,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6844,7 +6739,6 @@
       <c r="G107" t="n">
         <v>115</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6855,7 +6749,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6901,7 +6795,6 @@
       <c r="G108" t="n">
         <v>157</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6912,7 +6805,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6958,7 +6851,6 @@
       <c r="G109" t="n">
         <v>157</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -6969,7 +6861,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7015,7 +6907,6 @@
       <c r="G110" t="n">
         <v>134</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -7026,7 +6917,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7072,7 +6963,6 @@
       <c r="G111" t="n">
         <v>146</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -7083,7 +6973,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7129,7 +7019,6 @@
       <c r="G112" t="n">
         <v>115</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Scenic View</t>
@@ -7140,7 +7029,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/5/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
